--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260604.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>143,482</t>
+          <t>1,267,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,267,000</t>
+          <t>143,482</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,720,000</t>
+          <t>5,590,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,590,000</t>
+          <t>1,720,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,197,441</t>
+          <t>1,530,384</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,530,384</t>
+          <t>1,197,441</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>10,345,121</t>
+          <t>2,566,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,566,703</t>
+          <t>10,345,121</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,125,107</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>4,997,956</t>
+          <t>2,125,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>4,997,956</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,183,076</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>1,183,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,538,400</t>
+          <t>1,004,121</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>293,000</t>
+          <t>1,538,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,004,121</t>
+          <t>293,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
